--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:53</t>
+    <t xml:space="preserve">2026-09-10 01:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:04</t>
+    <t xml:space="preserve">2026-09-18 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:11</t>
+    <t xml:space="preserve">2026-09-23 14:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1057,7 +1057,9 @@
       <c r="C31" s="2" t="n">
         <v>7105</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" s="2" t="n">
+        <v>2022</v>
+      </c>
       <c r="E31" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:34</t>
+    <t xml:space="preserve">2026-10-02 15:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2022_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:44</t>
+    <t xml:space="preserve">2026-10-05 15:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
